--- a/report-2026-06-24.xlsx
+++ b/report-2026-06-24.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="1454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="1456">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-24T18:35:54+05:30</t>
+    <t>Generated 2026-06-24T18:41:12+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-24T18:33:53+05:30 (2m0s ago)</t>
+    <t>2026-06-24T18:39:12+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>Last error</t>
@@ -4372,10 +4372,16 @@
     <t>18:33:53.587</t>
   </si>
   <si>
+    <t>2026-06-24T18:38:55.500816+05:30</t>
+  </si>
+  <si>
+    <t>18:38:55.500</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-24T18:35:54+05:30</t>
+    <t>2026-06-24T18:41:12+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4970,7 +4976,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 19s</t>
+          <t>0h 7m 38s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -4990,7 +4996,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>25h 29m 19s</t>
+          <t>25h 31m 40s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -5000,7 +5006,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>18:35:54</t>
+          <t>18:41:12</t>
         </is>
       </c>
     </row>
@@ -5032,72 +5038,72 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>amd64</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>10.0.63</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>websocket</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>153315.5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>7775</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>10.0.64</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>disconnected</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>offline</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 17 10:41 PM</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-06-24 18:33:34</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25h 30m 40s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -5107,7 +5113,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>18:35:54</t>
+          <t>18:41:12</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5232,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-24T18:33:53.5871191+05:30</t>
+          <t>2026-06-24T18:38:55.500816+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5236,7 +5242,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18:33:53.587</t>
+          <t>18:38:55.500</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -41803,18 +41809,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="s">
+    <row r="715">
+      <c r="A715" s="4">
+        <v>698</v>
+      </c>
+      <c r="B715" s="4" t="s">
         <v>1451</v>
       </c>
-      <c r="B716" t="s">
+      <c r="C715" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D715" s="4" t="s">
         <v>1452</v>
       </c>
-      <c r="D716" t="s">
+      <c r="E715" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F715" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G715" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H715" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I715" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J715" s="4">
+        <v>0</v>
+      </c>
+      <c r="K715" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L715" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="s">
         <v>1453</v>
       </c>
-      <c r="E716">
-        <v>697</v>
+      <c r="B717" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D717" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E717">
+        <v>698</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-24.xlsx
+++ b/report-2026-06-24.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="1456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="1458">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-24T18:41:12+05:30</t>
+    <t>Generated 2026-06-24T18:46:07+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-24T18:39:12+05:30 (2m0s ago)</t>
+    <t>2026-06-24T18:44:28+05:30 (1m38s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>6</t>
   </si>
   <si>
     <t>Last error</t>
@@ -4378,10 +4378,16 @@
     <t>18:38:55.500</t>
   </si>
   <si>
+    <t>2026-06-24T18:43:55.312288+05:30</t>
+  </si>
+  <si>
+    <t>18:43:55.312</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-24T18:41:12+05:30</t>
+    <t>2026-06-24T18:46:07+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4976,7 +4982,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 38s</t>
+          <t>0h 12m 33s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -4996,7 +5002,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>25h 31m 40s</t>
+          <t>25h 35m 36s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -5006,7 +5012,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>18:41:12</t>
+          <t>18:46:07</t>
         </is>
       </c>
     </row>
@@ -5063,17 +5069,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>153315.5</t>
+          <t>145521.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -5083,7 +5089,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>655</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -5103,7 +5109,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>25h 30m 40s</t>
+          <t>25h 34m 25s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -5113,7 +5119,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>18:41:12</t>
+          <t>18:46:07</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5238,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-24T18:38:55.500816+05:30</t>
+          <t>2026-06-24T18:43:55.312288+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5242,7 +5248,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18:38:55.500</t>
+          <t>18:43:55.312</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -41847,18 +41853,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="s">
+    <row r="716">
+      <c r="A716" s="4">
+        <v>699</v>
+      </c>
+      <c r="B716" s="4" t="s">
         <v>1453</v>
       </c>
-      <c r="B717" t="s">
+      <c r="C716" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D716" s="4" t="s">
         <v>1454</v>
       </c>
-      <c r="D717" t="s">
+      <c r="E716" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F716" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G716" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H716" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I716" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J716" s="4">
+        <v>0</v>
+      </c>
+      <c r="K716" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L716" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="s">
         <v>1455</v>
       </c>
-      <c r="E717">
-        <v>698</v>
+      <c r="B718" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D718" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E718">
+        <v>699</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-24.xlsx
+++ b/report-2026-06-24.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-24T18:46:07+05:30</t>
+    <t>Generated 2026-06-24T18:46:28+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-24T18:44:28+05:30 (1m38s ago)</t>
+    <t>2026-06-24T18:44:28+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -4387,7 +4387,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-24T18:46:07+05:30</t>
+    <t>2026-06-24T18:46:28+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 33s</t>
+          <t>0h 12m 54s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>25h 35m 36s</t>
+          <t>25h 35m 56s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>18:46:07</t>
+          <t>18:46:28</t>
         </is>
       </c>
     </row>
@@ -5069,17 +5069,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>145521.5</t>
+          <t>145682.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>18:46:07</t>
+          <t>18:46:28</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-24.xlsx
+++ b/report-2026-06-24.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="1458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="1460">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-24T18:46:28+05:30</t>
+    <t>Generated 2026-06-24T18:51:14+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-24T18:44:28+05:30 (2m0s ago)</t>
+    <t>2026-06-24T18:49:46+05:30 (1m28s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>6</t>
+    <t>9</t>
   </si>
   <si>
     <t>Last error</t>
@@ -4384,10 +4384,16 @@
     <t>18:43:55.312</t>
   </si>
   <si>
+    <t>2026-06-24T18:48:55.3044114+05:30</t>
+  </si>
+  <si>
+    <t>18:48:55.304</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-24T18:46:28+05:30</t>
+    <t>2026-06-24T18:51:14+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4982,7 +4988,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 54s</t>
+          <t>0h 17m 40s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -5002,7 +5008,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>25h 35m 56s</t>
+          <t>25h 38m 27s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -5012,7 +5018,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>18:46:28</t>
+          <t>18:51:14</t>
         </is>
       </c>
     </row>
@@ -5069,17 +5075,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>243.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>145682.3</t>
+          <t>152887.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>16197</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -5089,7 +5095,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>972</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -5109,7 +5115,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>25h 34m 25s</t>
+          <t>25h 37m 6s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -5119,7 +5125,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>18:46:28</t>
+          <t>18:51:14</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5244,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-24T18:43:55.312288+05:30</t>
+          <t>2026-06-24T18:48:55.3044114+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5248,7 +5254,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18:43:55.312</t>
+          <t>18:48:55.304</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -41891,18 +41897,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="s">
+    <row r="717">
+      <c r="A717" s="4">
+        <v>700</v>
+      </c>
+      <c r="B717" s="4" t="s">
         <v>1455</v>
       </c>
-      <c r="B718" t="s">
+      <c r="C717" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D717" s="4" t="s">
         <v>1456</v>
       </c>
-      <c r="D718" t="s">
+      <c r="E717" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F717" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G717" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H717" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I717" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J717" s="4">
+        <v>0</v>
+      </c>
+      <c r="K717" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L717" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="s">
         <v>1457</v>
       </c>
-      <c r="E718">
-        <v>699</v>
+      <c r="B719" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D719" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E719">
+        <v>700</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-24.xlsx
+++ b/report-2026-06-24.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-24T18:51:14+05:30</t>
+    <t>Generated 2026-06-24T18:51:46+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-24T18:49:46+05:30 (1m28s ago)</t>
+    <t>2026-06-24T18:49:46+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -4393,7 +4393,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-24T18:51:14+05:30</t>
+    <t>2026-06-24T18:51:46+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 40s</t>
+          <t>0h 18m 12s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>25h 38m 27s</t>
+          <t>25h 39m 2s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>18:51:14</t>
+          <t>18:51:46</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>152887.5</t>
+          <t>152886.7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>24416</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>18:51:14</t>
+          <t>18:51:46</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-24.xlsx
+++ b/report-2026-06-24.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="1460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="1462">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-24T18:51:46+05:30</t>
+    <t>Generated 2026-06-24T18:56:15+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-24T18:49:46+05:30 (2m0s ago)</t>
+    <t>2026-06-24T18:55:04+05:30 (1m11s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>9</t>
+    <t>12</t>
   </si>
   <si>
     <t>Last error</t>
@@ -4390,10 +4390,16 @@
     <t>18:48:55.304</t>
   </si>
   <si>
+    <t>2026-06-24T18:54:15.6102674+05:30</t>
+  </si>
+  <si>
+    <t>18:54:15.610</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-24T18:51:46+05:30</t>
+    <t>2026-06-24T18:56:15+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4988,7 +4994,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 18m 12s</t>
+          <t>0h 22m 41s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -5008,7 +5014,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>25h 39m 2s</t>
+          <t>25h 41m 39s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -5018,7 +5024,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>18:51:46</t>
+          <t>18:56:15</t>
         </is>
       </c>
     </row>
@@ -5075,17 +5081,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>357.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>152886.7</t>
+          <t>153986.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>33365</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -5095,7 +5101,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -5115,7 +5121,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>25h 37m 6s</t>
+          <t>25h 40m 28s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -5125,7 +5131,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>18:51:46</t>
+          <t>18:56:15</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5250,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-24T18:48:55.3044114+05:30</t>
+          <t>2026-06-24T18:54:15.6102674+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5254,7 +5260,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18:48:55.304</t>
+          <t>18:54:15.610</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -41935,18 +41941,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" t="s">
+    <row r="718">
+      <c r="A718" s="4">
+        <v>701</v>
+      </c>
+      <c r="B718" s="4" t="s">
         <v>1457</v>
       </c>
-      <c r="B719" t="s">
+      <c r="C718" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D718" s="4" t="s">
         <v>1458</v>
       </c>
-      <c r="D719" t="s">
+      <c r="E718" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F718" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G718" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H718" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I718" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J718" s="4">
+        <v>0</v>
+      </c>
+      <c r="K718" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L718" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="s">
         <v>1459</v>
       </c>
-      <c r="E719">
-        <v>700</v>
+      <c r="B720" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D720" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E720">
+        <v>701</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-24.xlsx
+++ b/report-2026-06-24.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-24T18:56:15+05:30</t>
+    <t>Generated 2026-06-24T18:56:42+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-24T18:55:04+05:30 (1m11s ago)</t>
+    <t>2026-06-24T18:55:04+05:30 (1m38s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -4399,7 +4399,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-24T18:56:15+05:30</t>
+    <t>2026-06-24T18:56:42+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 22m 41s</t>
+          <t>0h 23m 7s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>25h 41m 39s</t>
+          <t>25h 42m 9s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>18:56:15</t>
+          <t>18:56:42</t>
         </is>
       </c>
     </row>
@@ -5081,17 +5081,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>357.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>153986.3</t>
+          <t>153842.1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>34174</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>18:56:15</t>
+          <t>18:56:42</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-24.xlsx
+++ b/report-2026-06-24.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-24T18:56:42+05:30</t>
+    <t>Generated 2026-06-24T18:57:04+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-24T18:55:04+05:30 (1m38s ago)</t>
+    <t>2026-06-24T18:55:04+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -4399,7 +4399,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-24T18:56:42+05:30</t>
+    <t>2026-06-24T18:57:04+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 23m 7s</t>
+          <t>0h 23m 29s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>25h 42m 9s</t>
+          <t>25h 42m 29s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>18:56:42</t>
+          <t>18:57:04</t>
         </is>
       </c>
     </row>
@@ -5081,17 +5081,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>323.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>153842.1</t>
+          <t>153985.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>34174</t>
+          <t>34840</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>18:56:42</t>
+          <t>18:57:04</t>
         </is>
       </c>
     </row>
